--- a/OKR_Cascade_Data_Input_final.xlsx
+++ b/OKR_Cascade_Data_Input_final.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zaggleprep-my.sharepoint.com/personal/abhishek_sukhadia_zaggle_in/Documents/KRA project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zaggleprep-my.sharepoint.com/personal/abhishek_sukhadia_zaggle_in/Documents/KRA project/OKR Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1029" documentId="8_{D48A80FA-5ACD-424F-9756-663FB617B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27FD73EB-F347-49BC-BFFA-88932B47C6EE}"/>
+  <xr:revisionPtr revIDLastSave="1041" documentId="8_{D48A80FA-5ACD-424F-9756-663FB617B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF1A28A6-429B-4903-AE91-D13D17BD6415}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Departments" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dept OKRs'!$A$1:$K$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dept OKRs'!$A$1:$L$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Org OKRs'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="502">
   <si>
     <t>OKR CASCADE - DATA INPUT TEMPLATE</t>
   </si>
@@ -115,9 +115,6 @@
     <t>Timeline</t>
   </si>
   <si>
-    <t>Zaggle will be the category-defining company in spend management. Win on product depth, platform stickiness, and expand within accounts.</t>
-  </si>
-  <si>
     <t>FY 2026-27</t>
   </si>
   <si>
@@ -130,9 +127,6 @@
     <t>EPIC-G</t>
   </si>
   <si>
-    <t>KR Description</t>
-  </si>
-  <si>
     <t>Measure</t>
   </si>
   <si>
@@ -497,10 +491,6 @@
   </si>
   <si>
     <t>Sum active products per client / # active clients</t>
-  </si>
-  <si>
-    <t>Achieve sustainable, customer led growth by maintaining Net Recurring Revenue (NRR) above 120%.
-(Starting ARR + Expansion - Contraction - Churn) / Starting ARR</t>
   </si>
   <si>
     <t>KR12</t>
@@ -1553,6 +1543,15 @@
   </si>
   <si>
     <t>Reduce Sales Cycle (Sales qualified to contract sign) by X% YoY</t>
+  </si>
+  <si>
+    <t>Achieve sustainable, customer led growth by maintaining Net Recurring Revenue (NRR) above 120%.</t>
+  </si>
+  <si>
+    <t>(Starting ARR + Expansion - Contraction - Churn) / Starting ARR (Existing Clients)</t>
+  </si>
+  <si>
+    <t>Key Result</t>
   </si>
 </sst>
 </file>
@@ -1737,6 +1736,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2169,15 +2172,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="48" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>152</v>
+        <v>499</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2210,761 +2213,761 @@
   <sheetData>
     <row r="1" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="10" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>76</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>120</v>
-      </c>
       <c r="J16" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="J18" s="9" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="K18" s="11"/>
     </row>
     <row r="19" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>127</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K19" s="11"/>
     </row>
     <row r="20" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K20" s="11"/>
     </row>
     <row r="21" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K21" s="11"/>
     </row>
     <row r="22" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3287,10 +3290,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FFF59E0B"/>
   </sheetPr>
-  <dimension ref="A1:K256"/>
+  <dimension ref="A1:L256"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3300,2899 +3303,2902 @@
     <col min="5" max="5" width="16" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="8" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="J19" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="F26" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="H26" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="9" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="9" t="s">
+      <c r="F30" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="K32" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="9" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="L32" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="G34" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H30" s="9" t="s">
+      <c r="H34" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F32" s="9" t="s">
+      <c r="K34" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="G32" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" s="9" t="s">
+      <c r="B35" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="G33" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F34" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="G34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>281</v>
-      </c>
       <c r="D35" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" s="9" t="str">
         <f>'Org OKRs'!A15</f>
         <v>ORG-4</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>282</v>
-      </c>
       <c r="C36" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>100</v>
+        <v>297</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" s="9" customFormat="1" ht="48" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="9" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E37" s="9" t="str">
         <f>'Org OKRs'!A16</f>
         <v>ORG-4</v>
       </c>
       <c r="F37" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="G37" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F40" s="9" t="s">
+      <c r="G40" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="G40" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>316</v>
-      </c>
       <c r="D41" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E41" s="9" t="str">
         <f>'Org OKRs'!A20</f>
         <v>ORG-6</v>
       </c>
       <c r="F41" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="K46" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="K47" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="9" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L52" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L53" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A54" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="K54" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L54" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L56" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="K61" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="K62" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L62" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A63" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="K64" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L64" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="L65" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="K66" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="L66" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="K67" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="J68" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="K68" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L68" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="K69" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="K70" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L70" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="K71" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A72" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="K72" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L72" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="K73" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A74" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F74" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="G41" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F42" s="9" t="s">
+      <c r="G74" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="K74" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="L74" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B75" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="G42" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="9" t="s">
+      <c r="C75" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="K75" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A76" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="K76" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L76" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A77" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="K77" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A78" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="K78" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A79" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="K79" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A80" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="G80" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="K47" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="K49" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" s="9" customFormat="1" ht="48" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="J50" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="J52" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="I53" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K53" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="J54" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K54" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="J55" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K55" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="J56" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K56" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="K58" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K59" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K60" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="I61" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K62" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="I63" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="J63" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E64" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="I64" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="J64" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K64" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="I65" s="9" t="s">
+      <c r="H80" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="K80" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="J65" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="I66" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="K66" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="I67" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="J67" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="I68" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="J68" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K68" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="I69" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="K69" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="I70" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="J70" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K70" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="J71" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K71" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="I72" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="J72" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K72" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="I73" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="J73" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K73" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="I74" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="J74" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="K74" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" s="9" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75" s="9" t="s">
+      <c r="L80" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A81" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F75" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="I75" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="J75" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E76" s="9" t="s">
+      <c r="H81" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="K81" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A82" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="G82" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F76" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H76" s="9" t="s">
+      <c r="H82" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="K82" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="I76" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="J76" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K76" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="I77" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="J77" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" s="9" customFormat="1" ht="36" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="I78" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="J78" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K78" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="I79" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="J79" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="K79" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="J80" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="K80" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="I81" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="J81" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" s="9" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="I82" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="J82" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="K82" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:11" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+      <c r="L82" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="97" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="98" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="99" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
@@ -6354,13 +6360,6 @@
     <row r="255" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="256" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:K82" xr:uid="{00000000-0001-0000-0300-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Revenue Operations"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6380,15 +6379,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
@@ -6396,7 +6395,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B3" s="6">
         <v>2</v>
@@ -6404,7 +6403,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B4" s="6">
         <v>3</v>
@@ -6412,7 +6411,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5" s="6">
         <v>4</v>
@@ -6420,7 +6419,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
@@ -6428,7 +6427,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B7" s="6">
         <v>6</v>
@@ -6436,7 +6435,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B8" s="6">
         <v>7</v>
@@ -6444,7 +6443,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" s="6">
         <v>8</v>
@@ -6452,7 +6451,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B10" s="6">
         <v>9</v>
@@ -6460,7 +6459,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B11" s="6">
         <v>10</v>

--- a/OKR_Cascade_Data_Input_final.xlsx
+++ b/OKR_Cascade_Data_Input_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zaggleprep-my.sharepoint.com/personal/abhishek_sukhadia_zaggle_in/Documents/KRA project/OKR Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1041" documentId="8_{D48A80FA-5ACD-424F-9756-663FB617B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF1A28A6-429B-4903-AE91-D13D17BD6415}"/>
+  <xr:revisionPtr revIDLastSave="1315" documentId="8_{D48A80FA-5ACD-424F-9756-663FB617B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A68889B-9AE2-47DE-ACBB-E13129FC9D17}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,8 @@
     <sheet name="Departments" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dept OKRs'!$A$1:$L$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Org OKRs'!$A$1:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dept OKRs'!$A$1:$M$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Org OKRs'!$A$1:$K$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="490">
   <si>
     <t>OKR CASCADE - DATA INPUT TEMPLATE</t>
   </si>
@@ -226,30 +226,9 @@
     <t>Sustain a Rule of 40 score above 40 while growing</t>
   </si>
   <si>
-    <t>Bring direct cost to revenue ratio down to below X (cloud, partners, 3P, CS, Impl)</t>
-  </si>
-  <si>
-    <t>Recover customer acquisition cost within X months</t>
-  </si>
-  <si>
-    <t>Deliver Rs. X revenue per employee (T12M)</t>
-  </si>
-  <si>
     <t>Keep Opex to Revenue ratio at or below X%</t>
   </si>
   <si>
-    <t>Revenue Growth Rate % + EBITDA Margin %</t>
-  </si>
-  <si>
-    <t>Fully loaded S&amp;M spend / (New ARR x Gross Margin)</t>
-  </si>
-  <si>
-    <t>T12M Revenue / Avg FTE count</t>
-  </si>
-  <si>
-    <t>(Net New ARR in Q x 4) / S&amp;M spend prior Q</t>
-  </si>
-  <si>
     <t>Total Opex / Total Revenue</t>
   </si>
   <si>
@@ -280,12 +259,6 @@
     <t>0.75 healthy, 1.0 excellent</t>
   </si>
   <si>
-    <t>Achieve a SaaS Magic Number of at least X</t>
-  </si>
-  <si>
-    <t>(Cloud/Infra + Partner Commissions + 3rd Party Integrations + Customer support + Implementation cost) / Revenue</t>
-  </si>
-  <si>
     <t>Reduce quarterly direct cost to serve to below Rs. X per active enterprise client</t>
   </si>
   <si>
@@ -298,12 +271,6 @@
     <t>Enterprise Sales, People &amp; Culture</t>
   </si>
   <si>
-    <t>Maintain regretted attrition of top performers at or below X% (rolling 12 months).</t>
-  </si>
-  <si>
-    <t>Voluntary exits of top-quartile / Avg top-quartile Head Count, rolling 12M</t>
-  </si>
-  <si>
     <t>Achieve an Employee NPS (eNPS) of at least X.</t>
   </si>
   <si>
@@ -346,18 +313,6 @@
     <t>&lt;X months</t>
   </si>
   <si>
-    <t>Achieve X% monthly AI adoption while improving output per FTE by Y% YoY.</t>
-  </si>
-  <si>
-    <t>(a) % monthly active AI users; (b) Output per FTE YoY %.</t>
-  </si>
-  <si>
-    <t>(a) &gt;=X%, (b) &gt;=Y%</t>
-  </si>
-  <si>
-    <t>Allocate at least X% of Engineering capacity to net-new innovation</t>
-  </si>
-  <si>
     <t>% Engineering capacity on innovation</t>
   </si>
   <si>
@@ -379,9 +334,6 @@
     <t>Reduce median time to market by X% YoY across S/M/L/XL features.</t>
   </si>
   <si>
-    <t xml:space="preserve">Median days from spec-approved to market release, by feature size. </t>
-  </si>
-  <si>
     <t>Maintain X% uptime and Y ms p95 latency on customer-facing services</t>
   </si>
   <si>
@@ -391,18 +343,12 @@
     <t>&gt;% , P95/99 ms</t>
   </si>
   <si>
-    <t>Avg days from signed to first recurring revenue</t>
-  </si>
-  <si>
     <t>Reduce Time to Go Live/First Value to at most X days</t>
   </si>
   <si>
     <t>&lt;X Days</t>
   </si>
   <si>
-    <t>Reach Client NPS of at least 40 (X)</t>
-  </si>
-  <si>
     <t>% Promoters - % Detractors</t>
   </si>
   <si>
@@ -430,21 +376,12 @@
     <t>Keep annualised Logo Churn at or below X%</t>
   </si>
   <si>
-    <t># accts cancelling / Total active accts (annualised)</t>
-  </si>
-  <si>
     <t>Grow Gross Total Revenue by X% YoY across products, channels and geographies</t>
   </si>
   <si>
-    <t>Total invoiced revenue</t>
-  </si>
-  <si>
     <t>Grow ARR by X% YoY</t>
   </si>
   <si>
-    <t>(ARR EOP / ARR prior EOP) - 1</t>
-  </si>
-  <si>
     <t>Reach X enterprise customers active in trailing 90 days by EOY-Y</t>
   </si>
   <si>
@@ -556,9 +493,6 @@
     <t>Achieve at least X% gross margin on every new deal, protecting against price-only wins</t>
   </si>
   <si>
-    <t>(ACV - direct delivery cost) / ACV</t>
-  </si>
-  <si>
     <t>Ship Sales Playbook v1.0 covering ICP, qualification, battle cards and pricing by FY-Y</t>
   </si>
   <si>
@@ -595,15 +529,9 @@
     <t>Avg days from qualified opp to closed-won</t>
   </si>
   <si>
-    <t>Grow Average Initial Client Value to Rs. X</t>
-  </si>
-  <si>
     <t>Total new logo revenue / # new logos</t>
   </si>
   <si>
-    <t>Multi-product initial rev / Total new logo rev</t>
-  </si>
-  <si>
     <t>Individual</t>
   </si>
   <si>
@@ -613,12 +541,6 @@
     <t># New logos</t>
   </si>
   <si>
-    <t>Inovice Rs. X in first-year ACV from new logos</t>
-  </si>
-  <si>
-    <t>Sum of first-year ACV, split one-time and recurring</t>
-  </si>
-  <si>
     <t>Rs X</t>
   </si>
   <si>
@@ -634,9 +556,6 @@
     <t># Products per Client</t>
   </si>
   <si>
-    <t>Invoice at least X% of new logo revenue from multi-product initial deals</t>
-  </si>
-  <si>
     <t>Marketing (Demand Gen)</t>
   </si>
   <si>
@@ -670,12 +589,6 @@
     <t>Revenue by source / Total revenue</t>
   </si>
   <si>
-    <t>Maintain qualified pipeline coverage at 3.0-4.0x of next-quarter target</t>
-  </si>
-  <si>
-    <t>Open pipeline / Next-Q target</t>
-  </si>
-  <si>
     <t>Build Rs. X White Space pipeline (UAE, SME)</t>
   </si>
   <si>
@@ -685,21 +598,9 @@
     <t>Improve Lead to Accepted Opportunity conversion to at least X%</t>
   </si>
   <si>
-    <t>Opps accepted / MQLs created</t>
-  </si>
-  <si>
-    <t>Grow to X active channel partners (deal in trailing 90D)</t>
-  </si>
-  <si>
-    <t># partners with a deal in trailing 90D</t>
-  </si>
-  <si>
     <t>Achieve Partner NPS of at least X (40+)</t>
   </si>
   <si>
-    <t>YoY: # analyst + events + media + social</t>
-  </si>
-  <si>
     <t>Generate Rs X MQLs and Rs Y SQLs in FY-Y</t>
   </si>
   <si>
@@ -745,16 +646,10 @@
     <t>Own forecast accuracy and keep pipeline data clean</t>
   </si>
   <si>
-    <t>T12M new logo revenue / Avg reps (12+ mo tenure)</t>
-  </si>
-  <si>
     <t>Bring Invoicing Error Rate to at most X%</t>
   </si>
   <si>
     <t># invoices with errors / Total invoices</t>
-  </si>
-  <si>
-    <t>Bill at least X% of invoices on time (within committed window)</t>
   </si>
   <si>
     <t># invoices on schedule / Total invoices</t>
@@ -785,69 +680,30 @@
     <t>KR26</t>
   </si>
   <si>
-    <t>PS-1</t>
-  </si>
-  <si>
     <t>PS-2</t>
   </si>
   <si>
     <t>PS-3</t>
   </si>
   <si>
-    <t>Set clear scope; A) separating standard configuration from custom build.  B) to minimise scope creep at implementation</t>
-  </si>
-  <si>
     <t>Understand customer pain through consultative discovery and propose winning solutions</t>
   </si>
   <si>
     <t>Carry voice of the customer back to Product for the roadmap</t>
   </si>
   <si>
-    <t>Reduce Avg Solutioning Cycle Time to at most X days per opportunity</t>
-  </si>
-  <si>
-    <t>Avg days from Solutioning request to proposal</t>
-  </si>
-  <si>
-    <t>Bring Solutioning Cost per Engaged Deal to at most Rs. X</t>
-  </si>
-  <si>
-    <t>Fully loaded Solutioning cost / # opps engaged</t>
-  </si>
-  <si>
     <t>Respond to every Solutioning request with a substantive first response within X hours</t>
   </si>
   <si>
     <t>Avg hours from request to first substantive response</t>
   </si>
   <si>
-    <t>Design multi-product solutions for at least X% of solutioned deals (ACV-weighted)</t>
-  </si>
-  <si>
-    <t>Multi-product deals / Total solutioned deals (ACV-weighted)</t>
-  </si>
-  <si>
-    <t>Deliver at least X% of deals with zero Solutioning-caused scope changes</t>
-  </si>
-  <si>
     <t>Deals with zero Solutioning miss / Total deals</t>
   </si>
   <si>
-    <t>Accept at least X% of customer feedback items into Product roadmap each quarter</t>
-  </si>
-  <si>
     <t>Feedback items accepted / Feedback items submitted per Q</t>
   </si>
   <si>
-    <t>Win at least X% of RFPs led by Solutioning</t>
-  </si>
-  <si>
-    <t>Won RFPs Solutioning led / Total RFPs responded</t>
-  </si>
-  <si>
-    <t>Rs X / Engaged Opportunity</t>
-  </si>
-  <si>
     <t>&lt; X Hrs</t>
   </si>
   <si>
@@ -893,55 +749,10 @@
     <t>Optimize and Increase product adoption, engagement. and retention</t>
   </si>
   <si>
-    <t>Leverage strategic product insights to directly improve overall win rates.</t>
-  </si>
-  <si>
     <t>PM-4</t>
   </si>
   <si>
-    <t>PM-5</t>
-  </si>
-  <si>
     <t>Customer Experience, Growth, Product</t>
-  </si>
-  <si>
-    <t>Ship X training manuals and enablement assets per quarter for internal teams and customers</t>
-  </si>
-  <si>
-    <t># manuals + assets released per Q</t>
-  </si>
-  <si>
-    <t>Ship X major releases per quarter per product</t>
-  </si>
-  <si>
-    <t>Reduce Product-Attributable churn to at most X% of ARR</t>
-  </si>
-  <si>
-    <t>Churned ARR classified 'product gap' / Total ARR</t>
-  </si>
-  <si>
-    <t>Keep post-release P0/P1 incidents plus product-gap tickets to at most X per 100 active accounts</t>
-  </si>
-  <si>
-    <t>(P0/P1 incidents + product-gap tickets) / (100 active accts/mo); weights TBD</t>
-  </si>
-  <si>
-    <t>Support Sales to reach at least X% win rate on qualified enterprise opportunities via product-market fit</t>
-  </si>
-  <si>
-    <t># resources created</t>
-  </si>
-  <si>
-    <t>Include AI-led capabilities in at least X% of releases</t>
-  </si>
-  <si>
-    <t># AI-led feature releases / Total releases</t>
-  </si>
-  <si>
-    <t># Story points released per product per quarter</t>
-  </si>
-  <si>
-    <t># Story Points Released in Qtr for each product</t>
   </si>
   <si>
     <t>Drive at least X% of user adoptions across &gt;80% of accounts
@@ -957,9 +768,6 @@
     <t>DAU/MAU Ratio, Session frequency per Client, No of Features used per client</t>
   </si>
   <si>
-    <t>Won opportunities / (Won + Lost) qualified</t>
-  </si>
-  <si>
     <t>KR34</t>
   </si>
   <si>
@@ -984,9 +792,6 @@
     <t>Own the product roadmap and sprint delivery, ship on cadence with Quality</t>
   </si>
   <si>
-    <t>Own the product roadmap and sprint delivery, ship on cadence with quality</t>
-  </si>
-  <si>
     <t>EG-1</t>
   </si>
   <si>
@@ -1012,9 +817,6 @@
   </si>
   <si>
     <t>Deliver at least X% of committed roadmap items on or before committed date</t>
-  </si>
-  <si>
-    <t># items delivered on/before date / Total committed</t>
   </si>
   <si>
     <t>Deliver at least X% of client-committed custom builds and integrations on customer-facing dates</t>
@@ -1045,9 +847,6 @@
     <t>&lt;X hours</t>
   </si>
   <si>
-    <t>Limit critical or high-severity production defects to a maximum of X per release.</t>
-  </si>
-  <si>
     <t># defects per release</t>
   </si>
   <si>
@@ -1163,9 +962,6 @@
     <t>Route at least X% of customer feedback items into Product roadmap each quarter</t>
   </si>
   <si>
-    <t>Maintain a baseline weekly Customer Issue Resolution Rate of X% or higher across all incoming support channels.</t>
-  </si>
-  <si>
     <t>Reduce the Average Ticket Resolution Time customer support tickets from [Baseline] hours to under X hours split by severity</t>
   </si>
   <si>
@@ -1226,15 +1022,9 @@
     <t>KR59</t>
   </si>
   <si>
-    <t>Deliver Net Revenue Retention of at least 120% (X) rolling 12M</t>
-  </si>
-  <si>
     <t>(Starting ARR + Expansion - Contraction - Churn) / Starting ARR</t>
   </si>
   <si>
-    <t>Achieve Account NPS of at least X (40+) via semi-annual relational surveys</t>
-  </si>
-  <si>
     <t>% Promoters - % Detractors (semi-annual)</t>
   </si>
   <si>
@@ -1244,24 +1034,6 @@
     <t>Renewed logos / Total logos up for renewal</t>
   </si>
   <si>
-    <t>Reach at least X% win rate on expansion opportunities</t>
-  </si>
-  <si>
-    <t>Build Rs. X in expansion pipeline</t>
-  </si>
-  <si>
-    <t>Invoiced Rs. X in Expansion ARR from cross-sell and upsell expansion</t>
-  </si>
-  <si>
-    <t>Sum cross-sell + upsell expansion ARR</t>
-  </si>
-  <si>
-    <t>Won expansion opportunities / (Won + Lost) expansion opportunities</t>
-  </si>
-  <si>
-    <t>Rs. value of expansion opportunities created</t>
-  </si>
-  <si>
     <t>KR60</t>
   </si>
   <si>
@@ -1292,12 +1064,6 @@
     <t>IM-3</t>
   </si>
   <si>
-    <t>Bring Implementation Cost per Go-Live to at most Rs. X</t>
-  </si>
-  <si>
-    <t>Fully loaded Impl team cost / # go-lives</t>
-  </si>
-  <si>
     <t>Ship Implementation Playbook v1.0 covering standard customer types, product flows and integration patterns by FY-Y</t>
   </si>
   <si>
@@ -1307,18 +1073,9 @@
     <t># certified / Total Impl team</t>
   </si>
   <si>
-    <t>Reduce Time to Go Live to at most X days (signed to first production transaction)</t>
-  </si>
-  <si>
-    <t>Avg days signed-to-first-txn, by complexity tier</t>
-  </si>
-  <si>
     <t>Meet at least X% of implementation timelines on committed customer dates (UAT/FUT/SUT)</t>
   </si>
   <si>
-    <t># delivered on/before committed date / Total, by complexity tier</t>
-  </si>
-  <si>
     <t>Realize at least X% of committed implementation revenue on schedule across active implementations</t>
   </si>
   <si>
@@ -1361,18 +1118,9 @@
     <t>KR71</t>
   </si>
   <si>
-    <t>&lt;Rs X per client</t>
-  </si>
-  <si>
     <t>&lt;X Days per client</t>
   </si>
   <si>
-    <t>Keep implementation stage churn rate to at most X% of signed deals</t>
-  </si>
-  <si>
-    <t># deals churned during implementation / Total signed</t>
-  </si>
-  <si>
     <t>Achieve Implementation CSAT of at least X% with at least Y% survey coverage</t>
   </si>
   <si>
@@ -1394,12 +1142,6 @@
     <t>KR41</t>
   </si>
   <si>
-    <t>KR72</t>
-  </si>
-  <si>
-    <t>KR73</t>
-  </si>
-  <si>
     <t>FO-1</t>
   </si>
   <si>
@@ -1440,27 +1182,6 @@
   </si>
   <si>
     <t>FO-7</t>
-  </si>
-  <si>
-    <t>KR74</t>
-  </si>
-  <si>
-    <t>KR75</t>
-  </si>
-  <si>
-    <t>KR76</t>
-  </si>
-  <si>
-    <t>KR77</t>
-  </si>
-  <si>
-    <t>KR78</t>
-  </si>
-  <si>
-    <t>KR79</t>
-  </si>
-  <si>
-    <t>KR80</t>
   </si>
   <si>
     <t>Ensure at least X% of Org and Departmental OKRs have leading indicator, named owner and cadenced review</t>
@@ -1545,13 +1266,257 @@
     <t>Reduce Sales Cycle (Sales qualified to contract sign) by X% YoY</t>
   </si>
   <si>
+    <t># of customer feedback items into Product roadmap each quarter</t>
+  </si>
+  <si>
+    <t>Feedback items accepted by product team</t>
+  </si>
+  <si>
+    <t>Deliver at least X% of deals with zero Solutioning-caused scope changes after client sign off</t>
+  </si>
+  <si>
+    <t>100% of product documentation (training manuals,PRDs and enablement assets) for every product for internal teams and customers</t>
+  </si>
+  <si>
+    <t>Number of completed docs / Total Required Docs</t>
+  </si>
+  <si>
+    <t>Reduce Time to Go Live to at most X days (BRD to Go Live)</t>
+  </si>
+  <si>
+    <t>Avg days BRD-to-Go Live, by complexity tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliver Net Recurring Revenue Retention of at least 120% (X) </t>
+  </si>
+  <si>
+    <t>Key Result</t>
+  </si>
+  <si>
     <t>Achieve sustainable, customer led growth by maintaining Net Recurring Revenue (NRR) above 120%.</t>
   </si>
   <si>
-    <t>(Starting ARR + Expansion - Contraction - Churn) / Starting ARR (Existing Clients)</t>
-  </si>
-  <si>
-    <t>Key Result</t>
+    <t>The percentage of recurring revenue retained from existing customers over a specific period. Formula: (Starting ARR + Expansion - Contraction - Churn) / Starting ARR</t>
+  </si>
+  <si>
+    <t>Revenue (ARR) Growth Rate % + EBITDA Margin %</t>
+  </si>
+  <si>
+    <t>The ruleof 40  provides a high-level view of a company's sustainability by balancing two competing objectives: growth and profitability. Growth rate includes revenue from both existing customers and new customers.</t>
+  </si>
+  <si>
+    <t>Direct costs refers to the expenses that can be directly attributed to each of our products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate the average number of active clients across all 12 months. </t>
+  </si>
+  <si>
+    <t>Achieve a CAC payback period of under [X] months through optimized sales funnels and increased initial contract values.</t>
+  </si>
+  <si>
+    <t>Fully loaded Sales &amp; Marketing spend / (New ARR x Gross Margin)</t>
+  </si>
+  <si>
+    <t>Gross margin is after deducting direct costs like cloud, partner channel margin, 3rd Party Integrations, Customer support, implementation etc.</t>
+  </si>
+  <si>
+    <t>(Cloud/Infra + Channel Partner Commissions + 3rd Party Integrations + Customer support + Implementation cost) / Revenue</t>
+  </si>
+  <si>
+    <t>Bring direct cost to revenue ratio down to below X (Technology, Commissions, Support and Implementation Costs)</t>
+  </si>
+  <si>
+    <t>Achieve an average revenue per employee of Rs. [X] by scaling automation and optimizing team productivity.</t>
+  </si>
+  <si>
+    <t>Gross Total Revenue / Avg FTE count</t>
+  </si>
+  <si>
+    <t>(Current Qtr ARR - Previous Qtr ARR) / S&amp;M spend prior Qtr</t>
+  </si>
+  <si>
+    <t>SaaS Magic Number measures your sales and marketing efficiency. It calculates how much new annual recurring revenue your company generates for every single dollar you spend on marketing and sales. Includes both new and existing account sales.</t>
+  </si>
+  <si>
+    <t>Achieve a SaaS Magic Number of at least X by expanding net new ARR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintain attrition of top performers at or below X% </t>
+  </si>
+  <si>
+    <t>Voluntary exits of top-quartile / Avg top-quartile Head Count</t>
+  </si>
+  <si>
+    <t>Regular internal employee surveys need to be done to calculate the employee NPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This includes but monetory and non-monetory recognitions. Eg. Non sales employees actively suggesting feature upsells, identifying expansion opportunities, getting leads, Going beyond the miles to provide customer excellence etc. </t>
+  </si>
+  <si>
+    <t>Allocate at least X% of Engineering capacity to new innovation/roadmap</t>
+  </si>
+  <si>
+    <t>Capacity can be measured based on man-hours, story points, etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median days from PRD approved to market release, by feature size. </t>
+  </si>
+  <si>
+    <t>Avg days from contract signed to Go live</t>
+  </si>
+  <si>
+    <t>Reach Client NPS of at least X</t>
+  </si>
+  <si>
+    <t>Measure customer loyalty, satisfaction, and enthusiasm for a Zaggle's products. They are willing to recommend zaggle to others</t>
+  </si>
+  <si>
+    <t>Each product will have its own utilization metrics. Eg. Based on invoices, transactions, users</t>
+  </si>
+  <si>
+    <t># accts Churned / Total active accts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This revenue includes both one-time and recurring revenue. </t>
+  </si>
+  <si>
+    <t>(Ending Gross Revenue EOP/ Starting Gross Revenue) - 1</t>
+  </si>
+  <si>
+    <t>(Ending ARR  / Starting ARR) - 1</t>
+  </si>
+  <si>
+    <t>Ending ARR = Starting ARR + New ARR + Expansion ARR + Contraction ARR - Churn ARR</t>
+  </si>
+  <si>
+    <t>Direct costs include cloud, channel partner commissions, 3rd Party Integrations, Customer support, implementation etc.</t>
+  </si>
+  <si>
+    <t>(ACV - direct cost) / ACV</t>
+  </si>
+  <si>
+    <t>Certifications based on standard product training and post-training evaluations. To be driven by Product and HR</t>
+  </si>
+  <si>
+    <t>Inovice Rs. X of total Revenue in first-year from new logos</t>
+  </si>
+  <si>
+    <t>Sum of first-year total revenue, split one-time and recurring</t>
+  </si>
+  <si>
+    <t>Revenue Targets for Sales</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Grow Average Initial Client Value (ACV) to Rs. X</t>
+  </si>
+  <si>
+    <t>Inbound Revenue - Customer reaches organically, via referrals, etc. Outbound Revenue - Cold Outreach via email marketing, cold calling, etc.</t>
+  </si>
+  <si>
+    <t>MQL - Marketing Qualified Lead
+SQL - Sales Qualified Lead</t>
+  </si>
+  <si>
+    <t>Maintain Sales qualified pipeline coverage at 3.0-4.0x of next-quarter target</t>
+  </si>
+  <si>
+    <t>Open SQL pipeline / Next-Q target</t>
+  </si>
+  <si>
+    <t>Ideal to measure both the amount and number of clients.</t>
+  </si>
+  <si>
+    <t>YoY: # analyst + events + media + social + AI Visibility</t>
+  </si>
+  <si>
+    <t>Measure each step in the funnel. Lead -&gt; MQL --&gt; SQL</t>
+  </si>
+  <si>
+    <t>Opportunities accepted (SQL) / Total Leads Generated</t>
+  </si>
+  <si>
+    <t>Grow to X active channel partners</t>
+  </si>
+  <si>
+    <t># partners with a deal</t>
+  </si>
+  <si>
+    <t>New logo revenue / Avg reps (12+ mo tenure)</t>
+  </si>
+  <si>
+    <t>Get at least X% of invoices billed on time</t>
+  </si>
+  <si>
+    <t>Hubspot adoption, ensuring all data entry in hubspot is accurate and properly maintained</t>
+  </si>
+  <si>
+    <t>Every AI feature should have an ROI attached</t>
+  </si>
+  <si>
+    <t>Deploy AI features that reduce user workflows/task completion time or achieve minimum CSAT of 80%</t>
+  </si>
+  <si>
+    <t># AI feature releases with certain ROI achieved</t>
+  </si>
+  <si>
+    <t>Successfully ship X% of planned quarterly roadmap releases on schedule, maintaining a 100% bug-free rate for critical defects (P0/P1) for two weeks post-launch</t>
+  </si>
+  <si>
+    <t># Story Points Released in Qtr for each product/ Total Story Points committed in planned roadmap</t>
+  </si>
+  <si>
+    <t>Every Product/Feature will have its own customer engagement metrics.</t>
+  </si>
+  <si>
+    <t>Every Product/Feature will have its own customer adoption metrics.</t>
+  </si>
+  <si>
+    <t>Limit critical or high-severity (P0) production defects to a maximum of X per release.</t>
+  </si>
+  <si>
+    <t>Revenue is measured via ACV for affected clients</t>
+  </si>
+  <si>
+    <t># Story Points delivered on/before date / Total committed</t>
+  </si>
+  <si>
+    <t>Maintain a baseline weekly Issue Resolution Rate of X% or higher across all incoming support channels.</t>
+  </si>
+  <si>
+    <t>The percentage of recurring revenue retained from existing customers over a specific period. Excludes new client ARR</t>
+  </si>
+  <si>
+    <t>Achieve Account NPS of at least X via semi-annual relational surveys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes All Enterprise clients up for renewal whether new or old. </t>
+  </si>
+  <si>
+    <t>Generate at least Rs X in total Expansion ARR through cross-sell and up-sell</t>
+  </si>
+  <si>
+    <t>Increase the average product-per-client ratio from X to Y across all active accounts.</t>
+  </si>
+  <si>
+    <t>Sum cross-sell + upsell expansion ARR + Add-ons ARR</t>
+  </si>
+  <si>
+    <t># delivered on/before committed date / Total, by complexity tier (within tolerance limit)</t>
+  </si>
+  <si>
+    <t>Ensure at least X% of all new closed-won customer accounts include 2 or more products at initial sign-on.</t>
+  </si>
+  <si>
+    <t># of multi-product new logo closed won / Total new logo Closed Won</t>
   </si>
 </sst>
 </file>
@@ -1690,7 +1655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1721,6 +1686,12 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1736,10 +1707,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2174,10 +2141,10 @@
     </row>
     <row r="2" spans="1:3" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>499</v>
+        <v>415</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>500</v>
+        <v>416</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>24</v>
@@ -2198,14 +2165,15 @@
   <sheetPr>
     <tabColor rgb="FFE8281A"/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="50" customWidth="1"/>
+    <col min="6" max="6" width="53.7109375" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
@@ -2222,16 +2190,16 @@
         <v>23</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>492</v>
+        <v>399</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>501</v>
+        <v>414</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>493</v>
+        <v>400</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>28</v>
@@ -2243,7 +2211,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="10" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>31</v>
       </c>
@@ -2257,20 +2225,22 @@
         <v>32</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G2" s="9"/>
+      <c r="G2" s="9" t="s">
+        <v>418</v>
+      </c>
       <c r="H2" s="9" t="s">
-        <v>65</v>
+        <v>417</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="10" customFormat="1" ht="48" x14ac:dyDescent="0.25">
@@ -2287,20 +2257,22 @@
         <v>35</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="9"/>
+        <v>425</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>419</v>
+      </c>
       <c r="H3" s="9" t="s">
-        <v>80</v>
+        <v>424</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -2317,23 +2289,25 @@
         <v>37</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>420</v>
+      </c>
       <c r="H4" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>31</v>
       </c>
@@ -2344,23 +2318,25 @@
         <v>24</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="9"/>
+        <v>421</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>423</v>
+      </c>
       <c r="H5" s="9" t="s">
-        <v>66</v>
+        <v>422</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -2374,26 +2350,26 @@
         <v>24</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>63</v>
+        <v>426</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>67</v>
+        <v>427</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>31</v>
       </c>
@@ -2404,23 +2380,25 @@
         <v>24</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -2434,23 +2412,23 @@
         <v>24</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -2464,23 +2442,23 @@
         <v>24</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>85</v>
+        <v>431</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
-        <v>86</v>
+        <v>432</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -2494,26 +2472,28 @@
         <v>24</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="9"/>
+        <v>76</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>433</v>
+      </c>
       <c r="H10" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="10" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>38</v>
       </c>
@@ -2524,53 +2504,55 @@
         <v>24</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="9"/>
+        <v>78</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>434</v>
+      </c>
       <c r="H11" s="9" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -2584,54 +2566,57 @@
         <v>24</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="G13" s="9"/>
+        <v>435</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>436</v>
+      </c>
       <c r="H13" s="9" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>105</v>
+        <v>437</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>141</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
@@ -2644,57 +2629,56 @@
         <v>24</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
-        <v>112</v>
+        <v>438</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="K15" s="11"/>
+        <v>101</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="16" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="9" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>58</v>
       </c>
@@ -2705,53 +2689,58 @@
         <v>24</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G17" s="9"/>
+        <v>439</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>440</v>
+      </c>
       <c r="H17" s="9" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G18" s="9"/>
+        <v>107</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>441</v>
+      </c>
       <c r="H18" s="9" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>388</v>
+        <v>124</v>
       </c>
       <c r="K18" s="11"/>
     </row>
@@ -2760,66 +2749,66 @@
         <v>59</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="9" t="s">
-        <v>126</v>
+        <v>442</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="K19" s="11"/>
     </row>
     <row r="20" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="K20" s="11"/>
     </row>
-    <row r="21" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>55</v>
@@ -2828,29 +2817,28 @@
         <v>24</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>121</v>
+        <v>33</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="K21" s="11"/>
+        <v>236</v>
+      </c>
     </row>
     <row r="22" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>55</v>
@@ -2859,28 +2847,31 @@
         <v>24</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G22" s="9"/>
+        <v>111</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>443</v>
+      </c>
       <c r="H22" s="9" t="s">
-        <v>127</v>
+        <v>444</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>286</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>55</v>
@@ -2889,29 +2880,31 @@
         <v>24</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G23" s="9"/>
+        <v>112</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>446</v>
+      </c>
       <c r="H23" s="9" t="s">
-        <v>131</v>
+        <v>445</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>55</v>
@@ -2920,55 +2913,36 @@
         <v>24</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="9" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="K24" s="11"/>
-    </row>
-    <row r="25" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>286</v>
-      </c>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
@@ -3199,16 +3173,16 @@
       <c r="J44" s="6"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="7"/>
@@ -3270,18 +3244,6 @@
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3293,7 +3255,7 @@
   <sheetPr>
     <tabColor rgb="FFF59E0B"/>
   </sheetPr>
-  <dimension ref="A1:L256"/>
+  <dimension ref="A1:M246"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3309,7 +3271,7 @@
     <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>40</v>
       </c>
@@ -3326,16 +3288,16 @@
         <v>42</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>492</v>
+        <v>399</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>501</v>
+        <v>414</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>493</v>
+        <v>400</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>28</v>
@@ -3346,8 +3308,11 @@
       <c r="L1" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="M1" s="15" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>34</v>
       </c>
@@ -3355,7 +3320,7 @@
         <v>43</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>24</v>
@@ -3367,30 +3332,36 @@
         <v>32</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>170</v>
+        <v>149</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>447</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>171</v>
+        <v>448</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>24</v>
@@ -3402,30 +3373,33 @@
         <v>35</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>24</v>
@@ -3437,310 +3411,343 @@
         <v>37</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>174</v>
+        <v>152</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>449</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>190</v>
+        <v>450</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>452</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>191</v>
+        <v>451</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>497</v>
+        <v>404</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>498</v>
+        <v>405</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>184</v>
+        <v>456</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>197</v>
+        <v>488</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>186</v>
+        <v>489</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>24</v>
@@ -3749,33 +3756,36 @@
         <v>31</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>24</v>
@@ -3784,418 +3794,466 @@
         <v>31</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>494</v>
+        <v>401</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>207</v>
+        <v>180</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>457</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>209</v>
+        <v>459</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>210</v>
+        <v>460</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>219</v>
+        <v>186</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>458</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>211</v>
+        <v>182</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>461</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>212</v>
+        <v>183</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>495</v>
+        <v>402</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>218</v>
+        <v>462</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>213</v>
+        <v>184</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>463</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>214</v>
+        <v>464</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>215</v>
+        <v>465</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>216</v>
+        <v>466</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>496</v>
+        <v>403</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>234</v>
+        <v>467</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>237</v>
+        <v>468</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>24</v>
@@ -4204,33 +4262,36 @@
         <v>31</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>24</v>
@@ -4239,666 +4300,737 @@
         <v>31</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>241</v>
+        <v>206</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>469</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>253</v>
+        <v>406</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>254</v>
+        <v>407</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>256</v>
+        <v>217</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>267</v>
+        <v>220</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="9" t="str">
+        <f>'Org OKRs'!A14</f>
+        <v>ORG-4</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="K31" s="14">
+        <v>1</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>251</v>
-      </c>
       <c r="D33" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="9" t="str">
+      <c r="E33" s="9" t="str">
         <f>'Org OKRs'!A15</f>
         <v>ORG-4</v>
       </c>
+      <c r="F33" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>59</v>
+      </c>
       <c r="F35" s="9" t="s">
-        <v>305</v>
+        <v>241</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>287</v>
+        <v>237</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>476</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M38" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M40" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M41" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H42" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="J42" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M42" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="9" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="J43" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="K43" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L36" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="9" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="9" t="str">
-        <f>'Org OKRs'!A16</f>
-        <v>ORG-4</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B38" s="9" t="s">
+      <c r="L43" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M44" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F45" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="G45" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L38" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L40" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="9" t="str">
-        <f>'Org OKRs'!A20</f>
-        <v>ORG-6</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H42" s="9" t="s">
+      <c r="C46" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="L44" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>329</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>24</v>
@@ -4907,33 +5039,36 @@
         <v>58</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>352</v>
+        <v>285</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>332</v>
+        <v>88</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M46" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>330</v>
+        <v>294</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>24</v>
@@ -4942,243 +5077,270 @@
         <v>58</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>339</v>
+        <v>302</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>449</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>338</v>
+        <v>303</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>340</v>
+        <v>87</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>329</v>
+        <v>295</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E48" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M48" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F48" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="L48" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>57</v>
-      </c>
       <c r="F49" s="9" t="s">
-        <v>355</v>
+        <v>288</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>343</v>
+        <v>480</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="K49" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M51" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L52" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M52" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="C53" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="L49" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" s="9" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="J50" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="L50" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="J52" s="9" t="s">
+      <c r="D53" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="J53" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="K52" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L52" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>368</v>
-      </c>
       <c r="K53" s="9" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>24</v>
@@ -5187,33 +5349,36 @@
         <v>58</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>360</v>
+        <v>293</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>369</v>
+        <v>482</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>370</v>
+        <v>326</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M54" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>24</v>
@@ -5222,983 +5387,700 @@
         <v>59</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>365</v>
+        <v>298</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>371</v>
+        <v>327</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>483</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>264</v>
+        <v>328</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="C56" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="L56" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M56" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M57" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M58" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M59" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M60" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="K61" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="K62" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L62" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M62" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A63" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="C63" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="J56" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="K56" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L56" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="K58" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="L58" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="K59" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="K60" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L60" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="K62" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L62" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>383</v>
-      </c>
       <c r="D63" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>428</v>
+        <v>347</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>401</v>
+        <v>343</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>402</v>
+        <v>344</v>
       </c>
       <c r="K63" s="9" t="s">
-        <v>407</v>
+        <v>87</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>429</v>
+        <v>348</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>403</v>
+        <v>346</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>98</v>
+        <v>360</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M64" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B65" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="L65" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="K66" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L66" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M66" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="K67" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="J68" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="K68" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L68" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="K69" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H70" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="G65" s="9" t="s">
+      <c r="J70" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="K70" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="L70" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H65" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="J65" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="L65" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="K66" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="J67" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="J68" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="K68" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L68" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="K69" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="L69" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="J70" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="K70" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L70" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>121</v>
-      </c>
       <c r="H71" s="9" t="s">
-        <v>442</v>
+        <v>387</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>443</v>
+        <v>388</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>98</v>
+        <v>396</v>
       </c>
       <c r="L71" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>414</v>
+        <v>378</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>437</v>
+        <v>356</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>98</v>
+        <v>395</v>
       </c>
       <c r="L72" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A73" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="J73" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="K73" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="J74" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="K74" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="L74" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="J75" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H76" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="J76" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="K76" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L76" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="C77" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M72" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="J77" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="J78" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="K78" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L78" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="J79" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="K79" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="J80" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="K80" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="L80" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A81" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="J81" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A82" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="J82" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="K82" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="L82" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:12" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="73" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="81" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="82" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="83" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="84" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="85" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="86" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="87" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="88" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="89" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="90" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="91" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="92" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="93" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="94" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="95" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
+    <row r="96" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="97" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="98" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="99" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
@@ -6349,17 +6231,8 @@
     <row r="244" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="245" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="246" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="247" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="248" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="249" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="250" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="251" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="252" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="253" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="254" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="255" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
-    <row r="256" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <autoFilter ref="A1:M72" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6395,7 +6268,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B3" s="6">
         <v>2</v>
@@ -6419,7 +6292,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
@@ -6427,7 +6300,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B7" s="6">
         <v>6</v>

--- a/OKR_Cascade_Data_Input_final.xlsx
+++ b/OKR_Cascade_Data_Input_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zaggleprep-my.sharepoint.com/personal/abhishek_sukhadia_zaggle_in/Documents/KRA project/OKR Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1315" documentId="8_{D48A80FA-5ACD-424F-9756-663FB617B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A68889B-9AE2-47DE-ACBB-E13129FC9D17}"/>
+  <xr:revisionPtr revIDLastSave="1318" documentId="8_{D48A80FA-5ACD-424F-9756-663FB617B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2428AA0E-CD0F-4CF5-A6AD-0C1DF88586BB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -832,9 +832,6 @@
 API latency p95/P99</t>
   </si>
   <si>
-    <t>Optimize infrastructure architecture to maximize performance-per-rupees and reduce operational waste.</t>
-  </si>
-  <si>
     <t>Elevate platform resilience and engineering quality standards to ensure uninterrupted user experiences.</t>
   </si>
   <si>
@@ -1296,9 +1293,6 @@
     <t>Achieve sustainable, customer led growth by maintaining Net Recurring Revenue (NRR) above 120%.</t>
   </si>
   <si>
-    <t>The percentage of recurring revenue retained from existing customers over a specific period. Formula: (Starting ARR + Expansion - Contraction - Churn) / Starting ARR</t>
-  </si>
-  <si>
     <t>Revenue (ARR) Growth Rate % + EBITDA Margin %</t>
   </si>
   <si>
@@ -1517,6 +1511,13 @@
   </si>
   <si>
     <t># of multi-product new logo closed won / Total new logo Closed Won</t>
+  </si>
+  <si>
+    <t>Cut cloud waste and upgrade our system setup to get more speed for every rupee we spend.</t>
+  </si>
+  <si>
+    <t>NRR means the percentage of recurring revenue retained from existing customers.
+Formula: (Starting ARR + Expansion - Contraction - Churn) / Starting ARR</t>
   </si>
 </sst>
 </file>
@@ -1707,6 +1708,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2141,10 +2146,10 @@
     </row>
     <row r="2" spans="1:3" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>416</v>
+        <v>489</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>24</v>
@@ -2190,16 +2195,16 @@
         <v>23</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>28</v>
@@ -2231,10 +2236,10 @@
         <v>60</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>68</v>
@@ -2260,13 +2265,13 @@
         <v>67</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>88</v>
@@ -2295,7 +2300,7 @@
         <v>72</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>73</v>
@@ -2324,13 +2329,13 @@
         <v>67</v>
       </c>
       <c r="F5" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>423</v>
-      </c>
       <c r="H5" s="9" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>89</v>
@@ -2356,11 +2361,11 @@
         <v>67</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>70</v>
@@ -2386,13 +2391,13 @@
         <v>67</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>71</v>
@@ -2448,11 +2453,11 @@
         <v>80</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>88</v>
@@ -2481,7 +2486,7 @@
         <v>76</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>77</v>
@@ -2513,7 +2518,7 @@
         <v>78</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>79</v>
@@ -2572,10 +2577,10 @@
         <v>95</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>90</v>
@@ -2608,7 +2613,7 @@
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>93</v>
@@ -2639,7 +2644,7 @@
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>101</v>
@@ -2695,10 +2700,10 @@
         <v>103</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>102</v>
@@ -2707,7 +2712,7 @@
         <v>104</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K17" s="11"/>
     </row>
@@ -2731,7 +2736,7 @@
         <v>107</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>108</v>
@@ -2765,7 +2770,7 @@
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>88</v>
@@ -2856,10 +2861,10 @@
         <v>111</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>115</v>
@@ -2889,10 +2894,10 @@
         <v>112</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>115</v>
@@ -3288,16 +3293,16 @@
         <v>42</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>28</v>
@@ -3309,7 +3314,7 @@
         <v>30</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3338,10 +3343,10 @@
         <v>149</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>87</v>
@@ -3350,7 +3355,7 @@
         <v>163</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3388,7 +3393,7 @@
         <v>163</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3417,7 +3422,7 @@
         <v>152</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>153</v>
@@ -3429,7 +3434,7 @@
         <v>163</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
@@ -3467,7 +3472,7 @@
         <v>163</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3493,13 +3498,13 @@
         <v>33</v>
       </c>
       <c r="H6" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>452</v>
-      </c>
       <c r="J6" s="9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>166</v>
@@ -3508,7 +3513,7 @@
         <v>163</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
@@ -3546,7 +3551,7 @@
         <v>163</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3584,7 +3589,7 @@
         <v>163</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3610,7 +3615,7 @@
         <v>33</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>160</v>
@@ -3622,7 +3627,7 @@
         <v>163</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3648,7 +3653,7 @@
         <v>33</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>161</v>
@@ -3660,7 +3665,7 @@
         <v>163</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3686,7 +3691,7 @@
         <v>33</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>162</v>
@@ -3698,7 +3703,7 @@
         <v>163</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3724,10 +3729,10 @@
         <v>33</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>170</v>
@@ -3736,7 +3741,7 @@
         <v>163</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3774,7 +3779,7 @@
         <v>163</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3800,7 +3805,7 @@
         <v>67</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>179</v>
@@ -3812,7 +3817,7 @@
         <v>163</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -3841,7 +3846,7 @@
         <v>180</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>181</v>
@@ -3853,7 +3858,7 @@
         <v>163</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3879,10 +3884,10 @@
         <v>33</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>190</v>
@@ -3891,7 +3896,7 @@
         <v>163</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3920,7 +3925,7 @@
         <v>186</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>187</v>
@@ -3932,7 +3937,7 @@
         <v>163</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3961,7 +3966,7 @@
         <v>182</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>183</v>
@@ -3973,7 +3978,7 @@
         <v>163</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3999,10 +4004,10 @@
         <v>33</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>192</v>
@@ -4011,7 +4016,7 @@
         <v>163</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4040,10 +4045,10 @@
         <v>184</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>87</v>
@@ -4052,7 +4057,7 @@
         <v>163</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4078,10 +4083,10 @@
         <v>33</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>191</v>
@@ -4090,7 +4095,7 @@
         <v>163</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4119,7 +4124,7 @@
         <v>185</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>193</v>
@@ -4128,7 +4133,7 @@
         <v>163</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4157,7 +4162,7 @@
         <v>207</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>209</v>
@@ -4166,7 +4171,7 @@
         <v>163</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4204,7 +4209,7 @@
         <v>163</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4230,7 +4235,7 @@
         <v>67</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>203</v>
@@ -4242,7 +4247,7 @@
         <v>163</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
@@ -4280,7 +4285,7 @@
         <v>163</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -4309,7 +4314,7 @@
         <v>206</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>208</v>
@@ -4321,7 +4326,7 @@
         <v>163</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4347,10 +4352,10 @@
         <v>95</v>
       </c>
       <c r="H28" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>406</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>407</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>104</v>
@@ -4359,7 +4364,7 @@
         <v>163</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4397,7 +4402,7 @@
         <v>163</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="30" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4423,7 +4428,7 @@
         <v>103</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>218</v>
@@ -4435,7 +4440,7 @@
         <v>163</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -4462,10 +4467,10 @@
         <v>80</v>
       </c>
       <c r="H31" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="J31" s="9" t="s">
         <v>409</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>410</v>
       </c>
       <c r="K31" s="14">
         <v>1</v>
@@ -4474,7 +4479,7 @@
         <v>163</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4500,13 +4505,13 @@
         <v>95</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I32" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>470</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>472</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>87</v>
@@ -4515,7 +4520,7 @@
         <v>163</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -4542,10 +4547,10 @@
         <v>95</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>87</v>
@@ -4554,7 +4559,7 @@
         <v>163</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -4583,7 +4588,7 @@
         <v>239</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>240</v>
@@ -4595,7 +4600,7 @@
         <v>163</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4624,7 +4629,7 @@
         <v>237</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>238</v>
@@ -4636,7 +4641,7 @@
         <v>163</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4647,7 +4652,7 @@
         <v>249</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>262</v>
+        <v>488</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>24</v>
@@ -4674,7 +4679,7 @@
         <v>163</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -4685,7 +4690,7 @@
         <v>250</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>24</v>
@@ -4712,7 +4717,7 @@
         <v>163</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -4723,7 +4728,7 @@
         <v>250</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>24</v>
@@ -4738,19 +4743,19 @@
         <v>103</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L38" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -4761,7 +4766,7 @@
         <v>250</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>24</v>
@@ -4776,19 +4781,19 @@
         <v>103</v>
       </c>
       <c r="H39" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="J39" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="J39" s="9" t="s">
-        <v>270</v>
-      </c>
       <c r="K39" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L39" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -4799,7 +4804,7 @@
         <v>251</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>24</v>
@@ -4814,19 +4819,19 @@
         <v>103</v>
       </c>
       <c r="H40" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="K40" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="J40" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>273</v>
-      </c>
       <c r="L40" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4837,7 +4842,7 @@
         <v>250</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>24</v>
@@ -4846,28 +4851,28 @@
         <v>58</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>256</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L41" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4878,7 +4883,7 @@
         <v>252</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>24</v>
@@ -4887,25 +4892,25 @@
         <v>57</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>95</v>
       </c>
       <c r="H42" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="J42" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="J42" s="9" t="s">
-        <v>277</v>
-      </c>
       <c r="K42" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L42" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="43" spans="1:13" s="9" customFormat="1" ht="48" x14ac:dyDescent="0.25">
@@ -4916,7 +4921,7 @@
         <v>250</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>24</v>
@@ -4931,19 +4936,19 @@
         <v>95</v>
       </c>
       <c r="H43" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="J43" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="J43" s="9" t="s">
+      <c r="K43" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="K43" s="9" t="s">
-        <v>281</v>
-      </c>
       <c r="L43" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="44" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4954,7 +4959,7 @@
         <v>252</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>24</v>
@@ -4963,7 +4968,7 @@
         <v>57</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>95</v>
@@ -4972,7 +4977,7 @@
         <v>257</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="K44" s="9" t="s">
         <v>87</v>
@@ -4981,7 +4986,7 @@
         <v>163</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="45" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4992,7 +4997,7 @@
         <v>252</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>24</v>
@@ -5001,7 +5006,7 @@
         <v>57</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>33</v>
@@ -5019,7 +5024,7 @@
         <v>163</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="46" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5027,10 +5032,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>24</v>
@@ -5039,16 +5044,16 @@
         <v>58</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>67</v>
       </c>
       <c r="H46" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="J46" s="9" t="s">
         <v>300</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>301</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>88</v>
@@ -5057,7 +5062,7 @@
         <v>163</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="47" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5065,10 +5070,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>24</v>
@@ -5077,19 +5082,19 @@
         <v>58</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>80</v>
       </c>
       <c r="H47" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="J47" s="9" t="s">
         <v>302</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>303</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>87</v>
@@ -5098,7 +5103,7 @@
         <v>163</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5106,10 +5111,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>24</v>
@@ -5118,13 +5123,13 @@
         <v>59</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G48" s="9" t="s">
         <v>95</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J48" s="9" t="s">
         <v>219</v>
@@ -5136,7 +5141,7 @@
         <v>163</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5144,10 +5149,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>24</v>
@@ -5156,16 +5161,16 @@
         <v>58</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>103</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>87</v>
@@ -5174,7 +5179,7 @@
         <v>163</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5182,10 +5187,10 @@
         <v>46</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>24</v>
@@ -5194,25 +5199,25 @@
         <v>58</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>103</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L50" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="51" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5220,10 +5225,10 @@
         <v>46</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>24</v>
@@ -5232,25 +5237,25 @@
         <v>58</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>103</v>
       </c>
       <c r="H51" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="J51" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="J51" s="9" t="s">
-        <v>310</v>
-      </c>
       <c r="K51" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L51" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="52" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5258,10 +5263,10 @@
         <v>46</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>24</v>
@@ -5270,16 +5275,16 @@
         <v>106</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>103</v>
       </c>
       <c r="H52" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="J52" s="9" t="s">
         <v>311</v>
-      </c>
-      <c r="J52" s="9" t="s">
-        <v>312</v>
       </c>
       <c r="K52" s="9" t="s">
         <v>87</v>
@@ -5288,7 +5293,7 @@
         <v>163</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="53" spans="1:13" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5296,10 +5301,10 @@
         <v>39</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>24</v>
@@ -5308,19 +5313,19 @@
         <v>59</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>103</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>87</v>
@@ -5329,7 +5334,7 @@
         <v>163</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5337,10 +5342,10 @@
         <v>39</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>24</v>
@@ -5349,16 +5354,16 @@
         <v>58</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>103</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K54" s="9" t="s">
         <v>87</v>
@@ -5367,7 +5372,7 @@
         <v>163</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="55" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5375,10 +5380,10 @@
         <v>39</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>24</v>
@@ -5387,19 +5392,19 @@
         <v>59</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>103</v>
       </c>
       <c r="H55" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="J55" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="J55" s="9" t="s">
-        <v>328</v>
       </c>
       <c r="K55" s="9" t="s">
         <v>87</v>
@@ -5408,7 +5413,7 @@
         <v>163</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5416,10 +5421,10 @@
         <v>39</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>24</v>
@@ -5428,25 +5433,25 @@
         <v>106</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="J56" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="J56" s="9" t="s">
-        <v>486</v>
-      </c>
       <c r="K56" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L56" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5454,10 +5459,10 @@
         <v>39</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>24</v>
@@ -5466,25 +5471,25 @@
         <v>106</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J57" s="9" t="s">
         <v>128</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L57" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5492,10 +5497,10 @@
         <v>48</v>
       </c>
       <c r="B58" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C58" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>334</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>24</v>
@@ -5504,13 +5509,13 @@
         <v>57</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>80</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J58" s="9" t="s">
         <v>151</v>
@@ -5522,7 +5527,7 @@
         <v>163</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="59" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5530,10 +5535,10 @@
         <v>48</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>24</v>
@@ -5542,16 +5547,16 @@
         <v>59</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>80</v>
       </c>
       <c r="H59" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="J59" s="9" t="s">
         <v>340</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>341</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>87</v>
@@ -5560,7 +5565,7 @@
         <v>163</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5568,10 +5573,10 @@
         <v>48</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>24</v>
@@ -5580,25 +5585,25 @@
         <v>57</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>103</v>
       </c>
       <c r="H60" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="J60" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="J60" s="9" t="s">
-        <v>412</v>
-      </c>
       <c r="K60" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L60" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="61" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5606,10 +5611,10 @@
         <v>48</v>
       </c>
       <c r="B61" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C61" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>334</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>24</v>
@@ -5618,16 +5623,16 @@
         <v>57</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>103</v>
       </c>
       <c r="H61" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="J61" s="9" t="s">
         <v>358</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>359</v>
       </c>
       <c r="K61" s="9" t="s">
         <v>87</v>
@@ -5636,7 +5641,7 @@
         <v>163</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="62" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5644,10 +5649,10 @@
         <v>48</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>24</v>
@@ -5656,16 +5661,16 @@
         <v>57</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K62" s="9" t="s">
         <v>87</v>
@@ -5674,7 +5679,7 @@
         <v>163</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="63" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5682,10 +5687,10 @@
         <v>48</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>24</v>
@@ -5694,16 +5699,16 @@
         <v>106</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H63" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="J63" s="9" t="s">
         <v>343</v>
-      </c>
-      <c r="J63" s="9" t="s">
-        <v>344</v>
       </c>
       <c r="K63" s="9" t="s">
         <v>87</v>
@@ -5712,7 +5717,7 @@
         <v>163</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5720,10 +5725,10 @@
         <v>48</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>24</v>
@@ -5732,25 +5737,25 @@
         <v>106</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H64" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="J64" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="J64" s="9" t="s">
-        <v>346</v>
-      </c>
       <c r="K64" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L64" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="65" spans="1:13" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -5758,10 +5763,10 @@
         <v>36</v>
       </c>
       <c r="B65" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>24</v>
@@ -5770,25 +5775,25 @@
         <v>31</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>67</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K65" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L65" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5796,10 +5801,10 @@
         <v>36</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>24</v>
@@ -5808,16 +5813,16 @@
         <v>31</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G66" s="9" t="s">
         <v>67</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K66" s="9" t="s">
         <v>87</v>
@@ -5826,7 +5831,7 @@
         <v>163</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5834,10 +5839,10 @@
         <v>36</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>24</v>
@@ -5846,25 +5851,25 @@
         <v>106</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G67" s="9" t="s">
         <v>95</v>
       </c>
       <c r="H67" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="J67" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="J67" s="9" t="s">
-        <v>382</v>
-      </c>
       <c r="K67" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L67" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="68" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5872,10 +5877,10 @@
         <v>36</v>
       </c>
       <c r="B68" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C68" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>24</v>
@@ -5884,16 +5889,16 @@
         <v>31</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G68" s="9" t="s">
         <v>67</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K68" s="9" t="s">
         <v>88</v>
@@ -5902,7 +5907,7 @@
         <v>163</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="69" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5910,10 +5915,10 @@
         <v>36</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>24</v>
@@ -5922,25 +5927,25 @@
         <v>56</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>95</v>
       </c>
       <c r="H69" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="K69" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="J69" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="K69" s="9" t="s">
-        <v>395</v>
-      </c>
       <c r="L69" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="70" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5948,10 +5953,10 @@
         <v>36</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>24</v>
@@ -5960,25 +5965,25 @@
         <v>56</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G70" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H70" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="J70" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="J70" s="9" t="s">
-        <v>386</v>
-      </c>
       <c r="K70" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L70" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M70" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="71" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5986,10 +5991,10 @@
         <v>36</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>24</v>
@@ -5998,25 +6003,25 @@
         <v>106</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G71" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H71" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="J71" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="J71" s="9" t="s">
-        <v>388</v>
-      </c>
       <c r="K71" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L71" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="72" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -6024,10 +6029,10 @@
         <v>36</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>24</v>
@@ -6036,25 +6041,25 @@
         <v>106</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L72" s="9" t="s">
         <v>163</v>
       </c>
       <c r="M72" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="73" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>

--- a/OKR_Cascade_Data_Input_final.xlsx
+++ b/OKR_Cascade_Data_Input_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zaggleprep-my.sharepoint.com/personal/abhishek_sukhadia_zaggle_in/Documents/KRA project/OKR Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1318" documentId="8_{D48A80FA-5ACD-424F-9756-663FB617B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2428AA0E-CD0F-4CF5-A6AD-0C1DF88586BB}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{3F1B79A4-771C-4CF7-ABA5-6F5B5D34CFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8DDC3FA-369E-4EDB-86FF-96D0944CEB82}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dept OKRs'!$A$1:$M$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Org OKRs'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Org OKRs'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="491">
   <si>
     <t>OKR CASCADE - DATA INPUT TEMPLATE</t>
   </si>
@@ -193,24 +193,6 @@
     <t>Pre-Sales &amp; Solutioning</t>
   </si>
   <si>
-    <t>Profitable revenue growth with cost optimization - efficient, sustainable scaling</t>
-  </si>
-  <si>
-    <t>Build a revenue-obsessed, engaged, AI-native, high-performance team</t>
-  </si>
-  <si>
-    <t>Embed AI across product, GTM and operations.</t>
-  </si>
-  <si>
-    <t>Faster implementation and delivery velocity, from contracting to revenue</t>
-  </si>
-  <si>
-    <t>Faster query resolution and reliable, dependable service</t>
-  </si>
-  <si>
-    <t>Grow the new base and expand installed base through cross-sell and upsell</t>
-  </si>
-  <si>
     <t>ORG-3</t>
   </si>
   <si>
@@ -250,21 +232,12 @@
     <t xml:space="preserve">&gt; 40 </t>
   </si>
   <si>
-    <t>&lt; X</t>
-  </si>
-  <si>
     <t>&gt; Rs. X</t>
   </si>
   <si>
     <t>0.75 healthy, 1.0 excellent</t>
   </si>
   <si>
-    <t>Reduce quarterly direct cost to serve to below Rs. X per active enterprise client</t>
-  </si>
-  <si>
-    <t>Total direct costs allocated / # active enterprise clients</t>
-  </si>
-  <si>
     <t>Marketing, Enterprise Sales</t>
   </si>
   <si>
@@ -277,12 +250,6 @@
     <t xml:space="preserve">% Promoters - % Detractors, quarterly survey. </t>
   </si>
   <si>
-    <t>Increase customer and revenue impact recognition rate by X% YoY.</t>
-  </si>
-  <si>
-    <t># recognitions tagged 'Customer Excellence' or 'Revenue Impact' per 100 employees</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -358,9 +325,6 @@
     <t>&gt;X</t>
   </si>
   <si>
-    <t>Active feature usage and stickiness across the product suite</t>
-  </si>
-  <si>
     <t>ORG-7</t>
   </si>
   <si>
@@ -385,12 +349,6 @@
     <t>Reach X enterprise customers active in trailing 90 days by EOY-Y</t>
   </si>
   <si>
-    <t># enterprise customers with revenue in trailing 90D + YoY %</t>
-  </si>
-  <si>
-    <t>&gt;X% , $ Y</t>
-  </si>
-  <si>
     <t>Every Function</t>
   </si>
   <si>
@@ -421,9 +379,6 @@
     <t>Customer Experience, Growth</t>
   </si>
   <si>
-    <t>Keep non-recurring revenue to at most X% of ARR</t>
-  </si>
-  <si>
     <t>Reach at least X Zaggle products active per enterprise client</t>
   </si>
   <si>
@@ -574,9 +529,6 @@
     <t>Generate qualified pipeline - own demand</t>
   </si>
   <si>
-    <t>Bring quarterly Cost per Accepted Opportunity to at most Rs. X</t>
-  </si>
-  <si>
     <t>Fully loaded Marketing spend / # accepted opps (per Q)</t>
   </si>
   <si>
@@ -598,12 +550,6 @@
     <t>Improve Lead to Accepted Opportunity conversion to at least X%</t>
   </si>
   <si>
-    <t>Achieve Partner NPS of at least X (40+)</t>
-  </si>
-  <si>
-    <t>Generate Rs X MQLs and Rs Y SQLs in FY-Y</t>
-  </si>
-  <si>
     <t>Rs MQLs,  Rs SQLs</t>
   </si>
   <si>
@@ -619,12 +565,6 @@
     <t># Channel Partners</t>
   </si>
   <si>
-    <t># marketing initiatives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X </t>
-  </si>
-  <si>
     <t>RO-1</t>
   </si>
   <si>
@@ -662,9 +602,6 @@
   </si>
   <si>
     <t>Achieve X% CRM hygiene and Y% weekly tool adoption across the team</t>
-  </si>
-  <si>
-    <t>Grow Revenue per Quota-Carrying Rep by X% YoY (12+ mo tenure) [Co-Owned with Sales]</t>
   </si>
   <si>
     <t xml:space="preserve"> # Fields Populated/Total Required Fields (% Data Completeness)
@@ -683,9 +620,6 @@
     <t>PS-2</t>
   </si>
   <si>
-    <t>PS-3</t>
-  </si>
-  <si>
     <t>Understand customer pain through consultative discovery and propose winning solutions</t>
   </si>
   <si>
@@ -1082,9 +1016,6 @@
     <t>Convert at least X% of customer change requests to billable revenue</t>
   </si>
   <si>
-    <t># change requests billed (Rs.) / # change requests raised</t>
-  </si>
-  <si>
     <t>KR62</t>
   </si>
   <si>
@@ -1124,9 +1055,6 @@
     <t># of 9 &amp; 10 rating responses/ total responses received for implementation</t>
   </si>
   <si>
-    <t>Rs X , &gt;X%</t>
-  </si>
-  <si>
     <t>Maximize implementation project profitability and secure immediate billing activation through rigorous scope management and milestone validation.</t>
   </si>
   <si>
@@ -1214,13 +1142,6 @@
     <t>Avg slippage days on business milestones</t>
   </si>
   <si>
-    <t># meeting cadence, #OKR checkins</t>
-  </si>
-  <si>
-    <t>Composite: % OKRs with (a) leading indicator (b) owner (c) reviewed on cadence
-% OKR Check ins, # OKR Cadence Meetings</t>
-  </si>
-  <si>
     <t>Publish at least X% of Org and departmental KPIs on dashboards with current data and named data owner</t>
   </si>
   <si>
@@ -1284,9 +1205,6 @@
     <t>Avg days BRD-to-Go Live, by complexity tier</t>
   </si>
   <si>
-    <t xml:space="preserve">Deliver Net Recurring Revenue Retention of at least 120% (X) </t>
-  </si>
-  <si>
     <t>Key Result</t>
   </si>
   <si>
@@ -1299,15 +1217,6 @@
     <t>The ruleof 40  provides a high-level view of a company's sustainability by balancing two competing objectives: growth and profitability. Growth rate includes revenue from both existing customers and new customers.</t>
   </si>
   <si>
-    <t>Direct costs refers to the expenses that can be directly attributed to each of our products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculate the average number of active clients across all 12 months. </t>
-  </si>
-  <si>
-    <t>Achieve a CAC payback period of under [X] months through optimized sales funnels and increased initial contract values.</t>
-  </si>
-  <si>
     <t>Fully loaded Sales &amp; Marketing spend / (New ARR x Gross Margin)</t>
   </si>
   <si>
@@ -1317,12 +1226,6 @@
     <t>(Cloud/Infra + Channel Partner Commissions + 3rd Party Integrations + Customer support + Implementation cost) / Revenue</t>
   </si>
   <si>
-    <t>Bring direct cost to revenue ratio down to below X (Technology, Commissions, Support and Implementation Costs)</t>
-  </si>
-  <si>
-    <t>Achieve an average revenue per employee of Rs. [X] by scaling automation and optimizing team productivity.</t>
-  </si>
-  <si>
     <t>Gross Total Revenue / Avg FTE count</t>
   </si>
   <si>
@@ -1335,18 +1238,12 @@
     <t>Achieve a SaaS Magic Number of at least X by expanding net new ARR</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintain attrition of top performers at or below X% </t>
-  </si>
-  <si>
     <t>Voluntary exits of top-quartile / Avg top-quartile Head Count</t>
   </si>
   <si>
     <t>Regular internal employee surveys need to be done to calculate the employee NPS</t>
   </si>
   <si>
-    <t xml:space="preserve">This includes but monetory and non-monetory recognitions. Eg. Non sales employees actively suggesting feature upsells, identifying expansion opportunities, getting leads, Going beyond the miles to provide customer excellence etc. </t>
-  </si>
-  <si>
     <t>Allocate at least X% of Engineering capacity to new innovation/roadmap</t>
   </si>
   <si>
@@ -1390,9 +1287,6 @@
   </si>
   <si>
     <t>Certifications based on standard product training and post-training evaluations. To be driven by Product and HR</t>
-  </si>
-  <si>
-    <t>Inovice Rs. X of total Revenue in first-year from new logos</t>
   </si>
   <si>
     <t>Sum of first-year total revenue, split one-time and recurring</t>
@@ -1429,9 +1323,6 @@
     <t>Ideal to measure both the amount and number of clients.</t>
   </si>
   <si>
-    <t>YoY: # analyst + events + media + social + AI Visibility</t>
-  </si>
-  <si>
     <t>Measure each step in the funnel. Lead -&gt; MQL --&gt; SQL</t>
   </si>
   <si>
@@ -1456,9 +1347,6 @@
     <t>Every AI feature should have an ROI attached</t>
   </si>
   <si>
-    <t>Deploy AI features that reduce user workflows/task completion time or achieve minimum CSAT of 80%</t>
-  </si>
-  <si>
     <t># AI feature releases with certain ROI achieved</t>
   </si>
   <si>
@@ -1507,17 +1395,134 @@
     <t># delivered on/before committed date / Total, by complexity tier (within tolerance limit)</t>
   </si>
   <si>
-    <t>Ensure at least X% of all new closed-won customer accounts include 2 or more products at initial sign-on.</t>
-  </si>
-  <si>
     <t># of multi-product new logo closed won / Total new logo Closed Won</t>
   </si>
   <si>
-    <t>Cut cloud waste and upgrade our system setup to get more speed for every rupee we spend.</t>
-  </si>
-  <si>
-    <t>NRR means the percentage of recurring revenue retained from existing customers.
+    <t>NRR is the percentage of recurring revenue retained from existing customers.
 Formula: (Starting ARR + Expansion - Contraction - Churn) / Starting ARR</t>
+  </si>
+  <si>
+    <t>Regrettable Attrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintain attrition of top performers at or below 10% </t>
+  </si>
+  <si>
+    <t>Productivity will be measured as Time or cost required before and after AI implementation</t>
+  </si>
+  <si>
+    <t>% hours or cost saved</t>
+  </si>
+  <si>
+    <t>Secure a company-wide ≥X% productivity gain in core AI-assisted workflows.</t>
+  </si>
+  <si>
+    <t>Direct costs refers to the expenses that can be directly attributed to each of our products. (Technology, Commissions, Support and Implementation Costs)</t>
+  </si>
+  <si>
+    <t>Bring "Direct Cost" to "Revenue" ratio to below X%</t>
+  </si>
+  <si>
+    <t>Bring Cost per Accepted Opportunity to at most Rs. X</t>
+  </si>
+  <si>
+    <t>Establish Zaggle as an AI-first fintech leader by embedding intelligence into our product ecosystem</t>
+  </si>
+  <si>
+    <t>Maximize profitable revenue growth by balancing unit economics and operational efficiency to achieve sustainable scaling.</t>
+  </si>
+  <si>
+    <t>Build a revenue-obsessed, AI-native, high-performance team, attracting and enabling the best talent.</t>
+  </si>
+  <si>
+    <t>Accelerate implementation and delivery velocity, ensuring faster contracting to revenue and dependable, reliable service.</t>
+  </si>
+  <si>
+    <t>Deliver world-class service reliability and fast resolutions to anchor customer trust.</t>
+  </si>
+  <si>
+    <t>X% Target</t>
+  </si>
+  <si>
+    <t># enterprise customers with revenue in trailing 90D,
+YoY %</t>
+  </si>
+  <si>
+    <t>Secure Rs X MQL and Rs Y SQL in Sales pipeline value</t>
+  </si>
+  <si>
+    <t>Third party tools - Hubspot</t>
+  </si>
+  <si>
+    <t>Analyst reports, events, media, social, AI Visibility all lead to increase in Share of Voice</t>
+  </si>
+  <si>
+    <t>Achieve Partner NPS of at least X</t>
+  </si>
+  <si>
+    <t>Deliver Net Recurring Revenue Retention of at least 120%</t>
+  </si>
+  <si>
+    <t>Deploy AI features that reduce user workflows/task completion time and achieve minimum CSAT of 80%</t>
+  </si>
+  <si>
+    <t># change requests billed / # change requests raised</t>
+  </si>
+  <si>
+    <t>&gt;X%
+(Also measure Change Request Revenue . Rs Y)</t>
+  </si>
+  <si>
+    <t>#OKR checkins</t>
+  </si>
+  <si>
+    <t>Composite: % OKRs with (a) leading indicator (b) owner (c) reviewed on cadence
+% OKR Check ins (Lagging), # OKR Cadence Meetings (Leading)</t>
+  </si>
+  <si>
+    <t>Make our products stickier by embedding Zaggle into our clients' daily and weekly financial habits.</t>
+  </si>
+  <si>
+    <t>Win new logos and expand existing accounts through aggressive market capture, cross-sell and upsell</t>
+  </si>
+  <si>
+    <t>Achieve a CAC payback period of under [X] months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achieve an average revenue per employee of Rs. [X] </t>
+  </si>
+  <si>
+    <t>Ensure at least X% of all new logos include 2 or more products at initial sign-on.</t>
+  </si>
+  <si>
+    <t>Cut cloud waste and optimize infra to get more for every rupee we spend.</t>
+  </si>
+  <si>
+    <t>PS-1</t>
+  </si>
+  <si>
+    <t>Keep non-recurring revenue to at least X% of ARR</t>
+  </si>
+  <si>
+    <t>YoY% Growth , (Also Track $ Y Target)</t>
+  </si>
+  <si>
+    <t>Invoice Rs. X of total Revenue in first-year from new logos</t>
+  </si>
+  <si>
+    <t>Optimize and Increase product adoption, engagement and retention</t>
+  </si>
+  <si>
+    <t>Grow Revenue per Quota-Carrying Rep by X% YoY (12+ mo tenure)</t>
+  </si>
+  <si>
+    <t>Individual, Co-Owned with Sales</t>
+  </si>
+  <si>
+    <t>&gt;120%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;X </t>
   </si>
 </sst>
 </file>
@@ -1708,10 +1713,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2146,10 +2147,10 @@
     </row>
     <row r="2" spans="1:3" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>24</v>
@@ -2170,7 +2171,7 @@
   <sheetPr>
     <tabColor rgb="FFE8281A"/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2195,16 +2196,16 @@
         <v>23</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>28</v>
@@ -2221,7 +2222,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>50</v>
+        <v>460</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>24</v>
@@ -2230,22 +2231,22 @@
         <v>32</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>416</v>
+        <v>389</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>415</v>
+        <v>388</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="10" customFormat="1" ht="48" x14ac:dyDescent="0.25">
@@ -2253,7 +2254,7 @@
         <v>31</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>50</v>
+        <v>460</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>24</v>
@@ -2262,22 +2263,22 @@
         <v>35</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>417</v>
+        <v>456</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -2285,7 +2286,7 @@
         <v>31</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>50</v>
+        <v>460</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>24</v>
@@ -2294,146 +2295,146 @@
         <v>37</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>72</v>
+        <v>478</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>73</v>
+        <v>390</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>50</v>
+        <v>460</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>50</v>
+        <v>460</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>424</v>
+        <v>55</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>425</v>
+        <v>56</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>50</v>
+        <v>461</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>427</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>50</v>
+        <v>461</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="9"/>
+        <v>452</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>451</v>
+      </c>
       <c r="H8" s="9" t="s">
-        <v>62</v>
+        <v>397</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -2441,29 +2442,31 @@
         <v>38</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>51</v>
+        <v>461</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="G9" s="9"/>
+        <v>67</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>398</v>
+      </c>
       <c r="H9" s="9" t="s">
-        <v>430</v>
+        <v>68</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -2471,471 +2474,451 @@
         <v>38</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>51</v>
+        <v>461</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="J10" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G11" s="9"/>
+      <c r="H11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="10" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>87</v>
-      </c>
       <c r="J11" s="9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>52</v>
+        <v>459</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>95</v>
-      </c>
       <c r="F12" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" s="9"/>
+        <v>399</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>400</v>
+      </c>
       <c r="H12" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>95</v>
-      </c>
       <c r="F14" s="9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="K14" s="11"/>
+        <v>90</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="15" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>53</v>
+        <v>463</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
-        <v>436</v>
+        <v>87</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>54</v>
+        <v>463</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="E16" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>437</v>
-      </c>
       <c r="G17" s="9" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>319</v>
+        <v>110</v>
       </c>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>105</v>
+        <v>476</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>439</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G18" s="9"/>
       <c r="H18" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="K18" s="11"/>
     </row>
     <row r="19" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>105</v>
+        <v>476</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="9" t="s">
-        <v>440</v>
+        <v>113</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="K19" s="11"/>
     </row>
-    <row r="20" spans="1:11" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>55</v>
+        <v>477</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>127</v>
+        <v>483</v>
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="9" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>104</v>
+        <v>464</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K20" s="11"/>
+        <v>214</v>
+      </c>
     </row>
     <row r="21" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>55</v>
+        <v>477</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G21" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>407</v>
+      </c>
       <c r="H21" s="9" t="s">
-        <v>109</v>
+        <v>408</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>236</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="K21" s="11"/>
     </row>
     <row r="22" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>55</v>
+        <v>477</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>55</v>
+        <v>477</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>444</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="G23" s="9"/>
       <c r="H23" s="9" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>115</v>
+        <v>484</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="K23" s="11"/>
-    </row>
-    <row r="24" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>236</v>
-      </c>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
@@ -3166,16 +3149,16 @@
       <c r="J43" s="6"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
@@ -3237,19 +3220,12 @@
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3266,8 +3242,8 @@
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="12" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="16" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" hidden="1" customWidth="1"/>
     <col min="8" max="9" width="50" customWidth="1"/>
@@ -3293,16 +3269,16 @@
         <v>42</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>28</v>
@@ -3314,7 +3290,7 @@
         <v>30</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>451</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3325,7 +3301,7 @@
         <v>43</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>24</v>
@@ -3337,25 +3313,25 @@
         <v>32</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>445</v>
+        <v>411</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3363,37 +3339,37 @@
         <v>34</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3401,40 +3377,40 @@
         <v>34</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>447</v>
+        <v>413</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
@@ -3442,37 +3418,37 @@
         <v>34</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3480,40 +3456,40 @@
         <v>34</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>450</v>
+        <v>415</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
@@ -3521,37 +3497,37 @@
         <v>34</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3559,37 +3535,37 @@
         <v>34</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3597,37 +3573,37 @@
         <v>34</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3635,37 +3611,37 @@
         <v>34</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3673,37 +3649,37 @@
         <v>34</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>454</v>
+        <v>419</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3711,48 +3687,48 @@
         <v>34</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>487</v>
+        <v>449</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>24</v>
@@ -3761,36 +3737,36 @@
         <v>31</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>177</v>
+        <v>458</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>24</v>
@@ -3799,341 +3775,344 @@
         <v>31</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>457</v>
+        <v>422</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>458</v>
+        <v>423</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>186</v>
+        <v>466</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>456</v>
+        <v>421</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>459</v>
+        <v>424</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>401</v>
+        <v>375</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>468</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>192</v>
+        <v>76</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>462</v>
+        <v>426</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>185</v>
+        <v>469</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>193</v>
+        <v>490</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4141,37 +4120,37 @@
         <v>47</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>207</v>
+        <v>487</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>163</v>
+        <v>488</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4179,37 +4158,37 @@
         <v>47</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4217,37 +4196,37 @@
         <v>47</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.25">
@@ -4255,10 +4234,10 @@
         <v>47</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>24</v>
@@ -4267,25 +4246,25 @@
         <v>31</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -4293,10 +4272,10 @@
         <v>47</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>24</v>
@@ -4305,28 +4284,28 @@
         <v>31</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4334,37 +4313,37 @@
         <v>49</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>212</v>
+        <v>482</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4372,37 +4351,37 @@
         <v>49</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4410,249 +4389,249 @@
         <v>49</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E31" s="9" t="str">
+        <f>'Org OKRs'!A13</f>
+        <v>ORG-4</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="K31" s="14">
+        <v>1</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="9" t="str">
         <f>'Org OKRs'!A14</f>
         <v>ORG-4</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="K31" s="14">
-        <v>1</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="9" t="str">
-        <f>'Org OKRs'!A15</f>
-        <v>ORG-4</v>
-      </c>
       <c r="F33" s="9" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>472</v>
+        <v>435</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>234</v>
+        <v>486</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>473</v>
+        <v>436</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>24</v>
@@ -4661,370 +4640,370 @@
         <v>31</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F38" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="K38" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="G38" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>266</v>
-      </c>
       <c r="L38" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="41" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>476</v>
+        <v>439</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="43" spans="1:13" s="9" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>477</v>
+        <v>440</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="45" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5032,37 +5011,37 @@
         <v>46</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="47" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5070,40 +5049,40 @@
         <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>447</v>
+        <v>413</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5111,37 +5090,37 @@
         <v>46</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="49" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5149,37 +5128,37 @@
         <v>46</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5187,37 +5166,37 @@
         <v>46</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="51" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5225,37 +5204,37 @@
         <v>46</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="52" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5263,37 +5242,37 @@
         <v>46</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="53" spans="1:13" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5301,40 +5280,40 @@
         <v>39</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>87</v>
+        <v>489</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="54" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5342,37 +5321,37 @@
         <v>39</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="55" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5380,40 +5359,40 @@
         <v>39</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5421,37 +5400,37 @@
         <v>39</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5459,37 +5438,37 @@
         <v>39</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>483</v>
+        <v>446</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5497,37 +5476,37 @@
         <v>48</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="59" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5535,37 +5514,37 @@
         <v>48</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5573,37 +5552,37 @@
         <v>48</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="61" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5611,37 +5590,37 @@
         <v>48</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="K61" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="62" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5649,37 +5628,37 @@
         <v>48</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="K62" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="63" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5687,75 +5666,75 @@
         <v>48</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="K63" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="9" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>48</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>345</v>
+        <v>472</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>359</v>
+        <v>473</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="65" spans="1:13" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -5763,10 +5742,10 @@
         <v>36</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>24</v>
@@ -5775,25 +5754,25 @@
         <v>31</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>390</v>
+        <v>475</v>
       </c>
       <c r="K65" s="9" t="s">
-        <v>389</v>
+        <v>474</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5801,10 +5780,10 @@
         <v>36</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>24</v>
@@ -5813,25 +5792,25 @@
         <v>31</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="K66" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5839,37 +5818,37 @@
         <v>36</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="68" spans="1:13" s="9" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -5877,10 +5856,10 @@
         <v>36</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>24</v>
@@ -5889,25 +5868,25 @@
         <v>31</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="K68" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="L68" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="69" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5915,37 +5894,37 @@
         <v>36</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="C69" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="K69" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="K69" s="9" t="s">
-        <v>394</v>
-      </c>
       <c r="L69" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="70" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5953,37 +5932,37 @@
         <v>36</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="G70" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M70" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="71" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5991,37 +5970,37 @@
         <v>36</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="G71" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="L71" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="72" spans="1:13" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -6029,37 +6008,37 @@
         <v>36</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="L72" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M72" s="9" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="73" spans="1:13" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
@@ -6237,7 +6216,6 @@
     <row r="245" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
     <row r="246" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:M72" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6273,7 +6251,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B3" s="6">
         <v>2</v>
@@ -6297,7 +6275,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
@@ -6305,7 +6283,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B7" s="6">
         <v>6</v>
